--- a/CIS 4374_Risk Register_Communication Plan.xlsx
+++ b/CIS 4374_Risk Register_Communication Plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\College Crap\Fall 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Stuff from D Drive\College Crap\Fall 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EF85D46-7BDF-4595-8DD7-0B4DCCD2C8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1912A9-28AE-42B3-A29E-5A86350CA07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5235" yWindow="5235" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{CD38FDB6-6E2D-4778-A292-BCE8E61031D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{CD38FDB6-6E2D-4778-A292-BCE8E61031D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Risk Register" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="73">
   <si>
     <t>ID</t>
   </si>
@@ -198,12 +198,6 @@
     <t>Video</t>
   </si>
   <si>
-    <t>Weekly Homework</t>
-  </si>
-  <si>
-    <t>Professor/Product Owner</t>
-  </si>
-  <si>
     <t>QA Testers</t>
   </si>
   <si>
@@ -219,16 +213,49 @@
     <t>Text Chat</t>
   </si>
   <si>
-    <t>Co-developers</t>
-  </si>
-  <si>
     <t>Project Deliverables</t>
   </si>
   <si>
-    <t>Individual Product Development</t>
-  </si>
-  <si>
-    <t>Share insight and knowledge</t>
+    <t>Product Owner</t>
+  </si>
+  <si>
+    <t>UI/UX Designer</t>
+  </si>
+  <si>
+    <t>Video/Text</t>
+  </si>
+  <si>
+    <t>Security Specialist</t>
+  </si>
+  <si>
+    <t>Product Visual Supervision</t>
+  </si>
+  <si>
+    <t>Product Security Supervision</t>
+  </si>
+  <si>
+    <t>Frontend Developer</t>
+  </si>
+  <si>
+    <t>Backend Developer</t>
+  </si>
+  <si>
+    <t>Frontend Product Development</t>
+  </si>
+  <si>
+    <t>Backend Product Development</t>
+  </si>
+  <si>
+    <t>Weekly Updates</t>
+  </si>
+  <si>
+    <t>Share Development Progress</t>
+  </si>
+  <si>
+    <t>Share insight on UI/UX design</t>
+  </si>
+  <si>
+    <t>Share insight on security developments</t>
   </si>
 </sst>
 </file>
@@ -270,7 +297,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -298,36 +325,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -364,8 +361,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC710925-C87E-48EA-84B7-B5870E583F8A}" name="Table3" displayName="Table3" ref="B2:F5" totalsRowShown="0">
-  <autoFilter ref="B2:F5" xr:uid="{FC710925-C87E-48EA-84B7-B5870E583F8A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC710925-C87E-48EA-84B7-B5870E583F8A}" name="Table3" displayName="Table3" ref="B2:F8" totalsRowShown="0">
+  <autoFilter ref="B2:F8" xr:uid="{FC710925-C87E-48EA-84B7-B5870E583F8A}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{11091D0F-2374-43DB-B2AE-21AA1ED78C44}" name="Stakeholders"/>
     <tableColumn id="2" xr3:uid="{503ABE56-64AD-4044-9F4A-26CF76443DE1}" name="Responsibilites"/>
@@ -1076,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842903B4-B281-4B3B-95EC-6B7470715578}">
-  <dimension ref="B2:F5"/>
+  <dimension ref="B2:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.85546875" customWidth="1"/>
@@ -1105,16 +1102,16 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
         <v>52</v>
@@ -1122,36 +1119,87 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
         <v>55</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>56</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>57</v>
-      </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>60</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>62</v>
       </c>
-      <c r="D5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
